--- a/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
+++ b/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts src drain" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps src drain" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts snk ingress" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps snk ingress" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1722,4 +1724,1122 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RAPIDS-beats SINK AXIS ingress -- signal contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The sink admits network beats through a per-channel reservation counter (r_pending_alloc) that is incremented on a REQUEST to an allocator whose grant signal is discarded. This sheet is the contract for that interface. NOTE: TASK-002 item 5 names this target 'credit/RDA accounting'; neither exists in the RTL -- there are zero word-boundary RDA references and no credit machinery (scheduler_beats.sv says 'No credit management'). The real decision surface is ingress admission, mapped here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Group / Channel</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Legal / Correct behavior (contract)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Key invariant - assertable check</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Notes / bug history</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Sink ingress / AXIS</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>s_axis_tready</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>snk_data_path_axis_beats</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>COMBINATIONAL: (fill_ready &amp;&amp; pending&gt;0) || fill_alloc_req. The second term carries NO fill_ready conjunct, so tready can assert while the channel FIFO is backpressuring.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>A beat accepted on AXIS must be stored. The only real store is fill_valid &amp;&amp; fill_ready (projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_unit_beats.sv:184-185, the FIFO's own wr_ready), so any accepted beat for which fill_ready was low is consumed off the network and lost.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:204-205 -- THE DEFECT CANDIDATE. See the K-map sheet for which cell and what is not yet established about reaching it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sink ingress / AXIS</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>fill_alloc_req</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>snk_data_path_axis_beats</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>s_axis_tvalid &amp;&amp; (r_pending_alloc[ch]==0) &amp;&amp; (fill_space_free[ch] &gt;= cfg_alloc_size). A request with NO handshake: alloc_ctrl_beats' wr_ready is discarded at the instantiation.</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>A reservation the allocator refuses must not be counted as granted. alloc_ctrl advances its pointer only on w_write &amp;&amp; !r_wr_full, so a request arriving while full is silently dropped -- but r_pending_alloc increments anyway.</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:189; discarded ready at projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_unit_beats.sv:126; allocator gating at projects/components/dmas/rapids/rtl/fub_beats/alloc_ctrl_beats.sv:76 and projects/components/dmas/rapids/rtl/fub_beats/alloc_ctrl_beats.sv:86.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sink ingress / accounting</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>r_pending_alloc[ch]</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>snk_data_path_axis_beats</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Per-channel count of beats allocated but not yet filled. Incremented by fill_alloc_size on the REQUEST, decremented by 1 per stored beat.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Must track the allocator's actual grants. It cannot: the increment is gated on fill_alloc_req alone, never on acceptance, and acceptance is not observable in this module.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:219-229. STREAM has no equivalent counter at all (zero occurrences in stream/rtl); it registers its alloc request and proves the contract instead -- projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:580, inside an `ifdef FORMAL` block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sink ingress / accounting</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>fill_space_free[ch]</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SCW</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>snk_sram_controller_unit_beats</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>The allocator's free-space view, REGISTERED one cycle to break a combinational path.</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>The space test is therefore one cycle stale. At cfg_alloc_size==1 line :222 leaves r_pending_alloc at 0, re-arming fill_alloc_req every cycle against that stale value.</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_unit_beats.sv:236. ALLOC_SIZE is an 8-bit rw CSR field defaulting to 0x10, so 1 is a writable value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Sink ingress / stats</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>dbg_axis_beats_received</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>snk_data_path_axis_beats</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Counts s_axis_tvalid &amp;&amp; s_axis_tready.</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Counts ACCEPTANCE, not storage -- so a beat lost by the tready term above is still counted as received.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:234.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>snk_data_path_axis_beats - AXIS ingress admission (projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Computed from a python mirror of the exact RTL expression (file:line cited, RTL quoted). Gray order 00 01 11 10; 1-cells green, 0-cells grey, unreachable cells X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TARGET: TASK-002 item 5, re-scoped. The first map is the one that matters: it shows an AXIS beat being accepted on a term that does not include the only signal that decides whether the beat can be stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>s_axis_tready  (AXIS beat accepted)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:204</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>s_axis_tready = (fill_ready &amp;&amp; (r_pending_alloc[ch] &gt; 0)) || fill_alloc_req</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rows = fill_ready/pending_gt0   cols = alloc_req</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: HEALTHY: every green cell would sit at fill_ready=1, because the only actual store is fill_valid &amp;&amp; fill_ready (projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_unit_beats.sv:184-185). ACTUAL: the single green cell at fill_ready=0 (alloc_req=1, pending_gt0=0) accepts an AXIS beat while the FIFO is backpressuring. The handshake completes, the beat is consumed off the network, and nothing stores it -- and projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:234 then counts it as received. NOT YET ESTABLISHED: whether that cell is reachable in practice. It needs fill_ready=0 simultaneously with fill_space_free &gt;= cfg_alloc_size, and those are two DIFFERENT counters -- the FIFO's own occupancy versus alloc_ctrl's allocation accounting (projects/components/dmas/rapids/rtl/fub_beats/alloc_ctrl_beats.sv:141), which is released only when data leaves the latency bridge. Proving or excluding that co-occurrence is the open question this map poses; a directed test driving AXIS into a backpressured channel would settle it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>fill_ready</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>the channel FIFO's own wr_ready, muxed per channel -- the ONLY signal that says the beat can actually be stored</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_unit_beats.sv:185</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>pending_gt0</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>r_pending_alloc[axis_channel_id] &gt; 0 -- this channel already holds a reservation</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:204</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>alloc_req</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>fill_alloc_req -- a fresh allocation is being requested this cycle</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:189</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    fill_alloc_req requires w_channel_needs_alloc, which is (r_pending_alloc[ch] == 0). So alloc_req and pending_gt0 cannot both be true: those cells are unreachable and marked X. This is why the defect cell necessarily sits at pending_gt0=0 -- it is the first beat of a packet, the exact case the RTL comment at :195-196 says the alloc term was added to protect.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:185, projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:189</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. cfg_alloc_size and the stale fill_space_free enter only through alloc_req; axis_channel_id selects WHICH channel's counters are read, not whether the beat is taken; tlast/tstrb/tdest ride the beat but cannot gate it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: alloc_req  |  fill_ready &amp; pending_gt0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (3 ones, 2 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      (fill_ready &amp; pending_gt0) | alloc_req</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>fill_valid  (beat offered to the FIFO)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:197</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>fill_valid = s_axis_tvalid &amp;&amp; ((r_pending_alloc[ch] &gt; 0) || (w_channel_needs_alloc &amp;&amp; w_channel_has_space))</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>rows = tvalid/pending_gt0   cols = needs_and_space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: This map is CORRECT and is included as the contrast. fill_valid omits fill_ready, which is right for a valid/ready producer -- the FIFO's wr_ready decides the transfer. The hazard is not here; it is that s_axis_tready (map 1) does NOT follow the same discipline, so the AXIS side and the FIFO side can disagree about whether the beat moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>tvalid</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>s_axis_tvalid -- the network is offering a beat</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:197</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>pending_gt0</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>r_pending_alloc[axis_channel_id] &gt; 0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:198</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>needs_and_space</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>w_channel_needs_alloc &amp;&amp; w_channel_has_space -- allocating this cycle instead</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:199</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    needs_and_space contains w_channel_needs_alloc = (r_pending_alloc[ch] == 0), so it cannot be true while pending_gt0 is. Those cells are unreachable and marked X.</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:185</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. The same channel-select and config terms as map 1 enter only through needs_and_space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: tvalid &amp; needs_and_space  |  tvalid &amp; pending_gt0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (2 ones, 2 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      tvalid &amp; (pending_gt0 | needs_and_space)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>r_pending_alloc credited</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:219</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>the += fill_alloc_size branch is taken on (fill_alloc_req &amp;&amp; fill_alloc_id == ch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>rows = alloc_req_ch/consume   cols = alloc_granted</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: The map is INDEPENDENT of alloc_granted, which is the finding. alloc_ctrl advances its pointer only on w_write &amp;&amp; !r_wr_full (projects/components/dmas/rapids/rtl/fub_beats/alloc_ctrl_beats.sv:76, projects/components/dmas/rapids/rtl/fub_beats/alloc_ctrl_beats.sv:86), so a request arriving while the allocator is full is silently dropped -- yet r_pending_alloc is credited the full fill_alloc_size regardless. The two green cells at alloc_granted=0 are where the datapath believes it holds space the allocator never gave it. HEALTHY would be a map that is 0 wherever alloc_granted=0, which requires routing wr_ready back -- it is driven and available, just not connected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>alloc_req_ch</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>fill_alloc_req targeting this channel</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:219</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>consume</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>fill_valid &amp;&amp; fill_ready &amp;&amp; fill_id == ch -- a beat is stored this cycle (selects the -1 variant, not whether we credit)</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:222</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>alloc_granted</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>alloc_ctrl's wr_ready = !r_wr_full -- whether the allocator ACTUALLY took the reservation. NOT AN INPUT: this wire is discarded at the instantiation</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/alloc_ctrl_beats.sv:137, discarded at projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_unit_beats.sv:126</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) alloc_granted is not observable from this module at all -- the port is left unconnected, so no cell can be excluded on its value. Recorded as an INDEPENDENCE note precisely because the independence IS the defect: an input that should constrain the decision has been made unable to.</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_unit_beats.sv:126</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. fill_alloc_size sets the SIZE of the credit, not whether it is taken; the per-channel loop index only selects which counter is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: alloc_req_ch</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      alloc_req_ch</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>STREAM vs RAPIDS: how each qualifies an allocation</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:580</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>RAPIDS' sink network side has no STREAM counterpart, so none of STREAM's proofs transfer here. That is exactly why TASK-002 ranks this the most exposed area, and it is the first sheet in this workbook with no fixed STREAM original to compare against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Concern</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>STREAM</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>RAPIDS-beats sink</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>local reservation counter</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>none (zero r_pending_alloc in stream/rtl)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>r_pending_alloc, credited on request (projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:225)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>allocation tied to an accepted handshake</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>yes, and PROVEN: alloc_req |-&gt; $past(arvalid &amp;&amp; arready) (projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:580, inside `ifdef FORMAL`)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>no property, and the allocator's wr_ready is discarded</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>ingress ready includes the store-enable</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>n/a -- stream's fill side is an AXI read engine, not an AXIS port</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>NO: s_axis_tready ORs in fill_alloc_req (projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_axis_beats.sv:204)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>allocator module</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>alloc_ctrl_beats -- byte-identical to stream's apart from the module name and subsystem comment</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
+++ b/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps src drain" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts snk ingress" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps snk ingress" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps sched commit" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2842,4 +2843,1179 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>scheduler_beats - completion gating and timeout escalation (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Computed from a python mirror of the exact RTL expression (file:line cited, RTL quoted). Gray order 00 01 11 10; 1-cells green, 0-cells grey, unreachable cells X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TARGET: TASK-002 item 4. Unlike the alloc/drain FUBs (byte-identical to STREAM's), this module DIVERGED: 1150 lines against STREAM's 1390. Map 1 is where the divergence lives, and it is the cone of the resolved wedge in projects/components/dmas/rapids/known_issues/resolved/snk_scheduler_write_commit_stall.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CH_XFER_DATA exit  (DATA descriptor)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:418</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>w_exec_complete = w_is_data ? w_transfer_complete : w_ctrl_complete, with w_transfer_complete = w_read_complete &amp;&amp; w_write_complete and w_write_complete = (r_write_beats_to_commit == 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rows = read_complete/write_issued   cols = write_committed/is_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: The map is INDEPENDENT of write_issued, which is the divergence. STREAM exits this state on ISSUE (projects/components/dmas/stream/rtl/fub/scheduler.sv:909, w_transfer_complete = w_read_complete &amp;&amp; w_write_issued) and defers the commit-wait to CH_COMPLETE, and only for the LAST descriptor (projects/components/dmas/stream/rtl/fub/scheduler.sv:542). RAPIDS waits for COMMITS here, on EVERY descriptor (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:776), and its CH_COMPLETE carries no commit gate at all. Two consequences. (1) Chain throughput: RAPIDS cannot advance to the next descriptor until the current one's B responses land; STREAM streams through. (2) A lost commit surfaces on ANY descriptor in RAPIDS rather than only the last. NOT a tolerance difference: under a lost commit NEITHER design recovers -- write_committed never reaches 1, no green cell is ever entered, the channel never reaches CH_IDLE and scheduler_idle (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:1105) never asserts. That is the wedge recorded in projects/components/dmas/rapids/known_issues/resolved/snk_scheduler_write_commit_stall.md (ILA: r_write_beats_to_commit=1, r_write_beats_remaining=0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>read_complete</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>r_read_beats_remaining == 0 -- all source beats read</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:771</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>write_issued</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>r_write_beats_remaining == 0 -- all destination beats ISSUED. This is STREAM's completion term; in RAPIDS it is NOT an input to this decision</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:902</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>write_committed</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>r_write_beats_to_commit == 0 -- all destination beats COMMITTED (B responses accounted)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:775</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>is_data</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>w_is_data -- DATA descriptor (control opcodes exit on w_ctrl_complete instead, outside this map)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:779</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    A beat can only commit after it has been issued, so committed &lt;= issued, hence r_write_beats_to_commit &gt;= r_write_beats_remaining. write_committed therefore IMPLIES write_issued, and cells with write_committed=1 and write_issued=0 are unreachable and marked X. This is exactly why waiting on commits is strictly later than waiting on issues, never earlier.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:775, projects/components/dmas/stream/rtl/fub/scheduler.sv:902</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four for a DATA descriptor. The timeout path reaches the FSM through a separate w_hard_error/w_timeout_escalate branch evaluated BEFORE this case (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:978); channel reset overrides both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: read_complete &amp; write_committed &amp; is_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      is_data &amp; read_complete &amp; write_committed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>sched_wr_valid  (request more writes)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:858</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>sched_wr_valid = (state == CH_XFER_DATA) &amp;&amp; w_is_data &amp;&amp; (r_write_beats_remaining != 0) &amp;&amp; !w_write_complete &amp;&amp; !w_sched_wr_completing_this_cycle &amp;&amp; !w_wr_need_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>rows = xfer_and_data/beats_to_issue   cols = write_committed/completing_now   pages = need_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: The issue-count gate is what stops a spurious garbage AW during the commit-wait (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:853-857). Note the !w_write_complete term is LOGICALLY REDUNDANT here: beats_to_issue=1 already forces write_committed=0 (see the relation), so it can never be the deciding term -- every cell where it would matter is marked X. It is belt-and-braces, not live logic, and a future reader should not assume removing it changes behaviour. STREAM carries the same 5-term conjunction with a near-identical comment (projects/components/dmas/stream/rtl/fub/scheduler.sv:1004-1008), so this gate did NOT diverge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>xfer_and_data</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>r_current_state == CH_XFER_DATA &amp;&amp; w_is_data</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:858</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>beats_to_issue</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>r_write_beats_remaining != 0 -- the explicit issue-count gate</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:859</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>write_committed</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>w_write_complete -- all beats committed</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:860</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>completing_now</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>w_sched_wr_completing_this_cycle -- look-ahead de-assert</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:861</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>need_base</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>w_wr_need_base -- TASK-101 run-boundary stall</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:862</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    r_write_beats_to_commit &gt;= r_write_beats_remaining always (commits trail issues), so beats_to_issue (remaining != 0) implies to_commit != 0, i.e. write_committed = 0. Cells with both beats_to_issue=1 and write_committed=1 are unreachable and marked X.</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:775, projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:859</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these five. sched_wr_addr/beats are payload, not qualifiers; sched_wr_ready is the engine's backpressure and deliberately does not gate the request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>[need_base=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>[need_base=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: xfer_and_data &amp; beats_to_issue &amp; !completing_now &amp; !need_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 8 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      xfer_and_data &amp; beats_to_issue &amp; ~write_committed &amp; ~completing_now &amp; ~need_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>w_timeout_escalate  (soft -&gt; fatal)</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:970</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>w_timeout_escalate = (cfg_sched_timeout_limit != 0) &amp;&amp; (r_timeout_strikes &gt;= cfg_sched_timeout_limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>rows = timeout_enable/counter_expired   cols = limit_nonzero/strikes_at_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Escalation drives the channel into sticky CH_ERROR (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:380), so the green cells are fatal transitions. The map is INDEPENDENT of timeout_enable, and that is worth a look: strikes are cleared only by channel reset, by reaching CH_IDLE, or by real write progress (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:932-936) -- never by the enable bit going low. So a channel that has already accumulated strikes and then has cfg_sched_timeout_enable cleared by software still has w_timeout_escalate asserted and still wedges into CH_ERROR. NOT YET ESTABLISHED whether any host sequence actually clears enable mid-transfer; the map states the exposure rather than asserting the bug. A directed test that raises strikes, clears enable, and checks the channel does not enter CH_ERROR would settle it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>timeout_enable</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>cfg_sched_timeout_enable -- the feature's enable bit; gates w_timeout_expired, which is the ONLY thing that increments strikes</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:965</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>counter_expired</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>r_timeout_counter &gt;= cfg_sched_timeout_cycles -- this window elapsed</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:966</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>limit_nonzero</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>cfg_sched_timeout_limit != 0 -- escalation armed (0 = never escalate, pure soft timeout)</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:970</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>strikes_at_limit</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>r_timeout_strikes &gt;= cfg_sched_timeout_limit -- enough consecutive windows with no write progress</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:971</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (r_timeout_strikes &gt;= cfg_sched_timeout_limit) is unconditionally TRUE when cfg_sched_timeout_limit is 0, because the counter is unsigned. So limit_nonzero=0 forces strikes_at_limit=1, and cells with both 0 are unreachable and marked X. This is precisely why the explicit != 0 guard exists: without it, disabling escalation would enable it.</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:970, projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:971</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four. cfg_sched_timeout_cycles enters only through counter_expired; the counter's own 4-way arming priority (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:920-928) decides WHEN a window elapses, not whether escalation fires once strikes are banked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: limit_nonzero &amp; strikes_at_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (4 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      limit_nonzero &amp; strikes_at_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>STREAM vs RAPIDS scheduler: where the commit-wait sits</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:418</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>The alloc/drain FUBs are byte-identical between the two projects; this scheduler is not. The divergence is narrow -- one term in the completion wire and the placement of the commit-wait -- but it changes chain behaviour and which descriptor exposes a lost commit. Neither side has a recovery path; see projects/components/dmas/rapids/known_issues/resolved/snk_scheduler_write_commit_stall.md, whose section 6a found the write engine byte-identical and therefore the under-count risk shared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Concern</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>STREAM scheduler.sv (1390 lines)</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>RAPIDS scheduler_beats.sv (1150 lines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>CH_XFER_DATA exit term</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>w_write_issued -- issue-based (projects/components/dmas/stream/rtl/fub/scheduler.sv:909)</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>w_write_complete -- commit-based (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:776)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>formal property asserts</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>(w_read_complete &amp;&amp; w_write_issued) (projects/components/dmas/stream/rtl/fub/scheduler.sv:1376)</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>(w_read_complete &amp;&amp; w_write_complete) (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:1136)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>CH_COMPLETE commit gate</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>yes, last descriptor only (projects/components/dmas/stream/rtl/fub/scheduler.sv:542); chained advances immediately</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>none (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:424-432)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>chain streams without waiting for B</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>no -- every descriptor waits for commits</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>recovers from a lost commit</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>no -- hangs in CH_COMPLETE</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>no -- hangs in CH_XFER_DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>sched_wr_valid issue-count gate</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>same 5 terms (projects/components/dmas/stream/rtl/fub/scheduler.sv:1004-1008)</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>same 5 terms (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:858-862)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
+++ b/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts snk ingress" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps snk ingress" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps sched commit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts snk errors" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K-maps snk errors" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4018,4 +4020,1571 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RAPIDS-beats SINK error reporting and drain port -- signal contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TASK-002 items 1 and 2. Item 1: the write engine detects bad B responses per channel and the sink throws that detection away, leaving two fatal-error terms provably dead. Item 2: the sink SRAM drain port serves one channel per cycle by construction. Both were filed against retired pre-beats files, so only their anchors were stale; see projects/components/dmas/rapids/known_issues/active/sink_data_path.md and projects/components/dmas/rapids/known_issues/active/sink_sram_control.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Group / Channel</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Legal / Correct behavior (contract)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Key invariant - assertable check</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Notes / bug history</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Sink errors / engine</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>sched_wr_error (engine output)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>axi_write_engine_beats</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Sticky per-channel flag, set on any B beat whose response is not OKAY: m_axi_bvalid &amp;&amp; m_axi_bready &amp;&amp; (m_axi_bresp != 2'b00), channel taken from BID.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>A SLVERR or DECERR on a write response must reach the channel FSM and fault the channel. It does not, on the sink.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:951 sets it, :955 latches per channel, :964 drives the port declared at :144. The detection is REAL and complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sink errors / plumbing</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>sched_wr_error (macro net)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>rapids_snk_beats</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Tied to a constant: `assign sched_wr_error = '0;` with the comment "TODO: Add when write engine supports error reporting".</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>The TODO's stated reason is FALSE -- the engine has supported error reporting all along (see the row above). This net is what the scheduler actually sees.</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680, consumed at :514 by the scheduler_group_array_beats instantiated at :344.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sink errors / plumbing</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>sched_rd_error (macro net)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>rapids_snk_beats</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Tied to '0 at the instantiation.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>LEGITIMATE: the sink has no AXI read engine, and its read done-strobes are tied off in the same block. Listed so a reader does not mistake it for the same defect as the row above.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:513. Contrast projects/components/dmas/rapids/rtl/macro_beats/rapids_src_beats.sv:491, where the SOURCE wires a real sched_rd_error, and :492 where the source ties its unused write error off for the mirror-image legitimate reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sink errors / scheduler</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>r_write_error_sticky</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>scheduler_beats</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Latched high on any cycle sched_wr_error is high; cleared on reset and channel reset.</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Constant 0 on the sink, because its only source is the tied-off net. Feeds w_hard_error AND the MonBus error packet, so the sink's error telemetry is dead too.</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:944 latches it, :979 uses it in w_hard_error, :1084 packs it into a monitor packet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Sink errors / scheduler</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>w_hard_error</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>scheduler_beats</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>7-term OR: descriptor_error, sched_rd_error, sched_wr_error, both stickies, and the two control-engine error terms. Drives the sticky CH_ERROR transition.</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>On the sink, 4 of the 7 terms are constant 0. For a DATA descriptor it reduces to descriptor_error alone.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:978-980, consumed at :380. Live terms come from projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_beats.sv:264 (descriptor_engine_beats) and projects/components/dmas/rapids/rtl/fub/ctrlrd_engine.sv:437.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Sink SRAM / drain port</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>drain_read / drain_id</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>1 / CIW</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>snk_sram_controller_beats</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>A single read strobe and a single channel index, decoded one-hot to select which channel is drained, with one data mux on the same index.</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>At most one channel can be drained per cycle, by construction. This is the interface, not an omission inside the module.</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147-148 decode, :157 mux. See projects/components/dmas/rapids/known_issues/active/sink_sram_control.md -- the limitation is structural, which is why a keyword search for "single read" finds nothing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rapids_snk_beats / scheduler_beats - fatal-error entry (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:978)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Computed from a python mirror of the exact RTL expression (file:line cited, RTL quoted). Gray order 00 01 11 10; 1-cells green, 0-cells grey, unreachable cells X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TARGET: TASK-002 items 1 and 2. READ THE X CELLS FIRST. Normally a don't-care marks a state that cannot physically occur. Here most of map 1 is X because inputs were tied to constants at an instantiation -- two legitimately, two by defect. The don't-cares ARE the finding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>w_hard_error  (on the SINK instance)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:978</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>w_hard_error = descriptor_error || sched_rd_error || sched_wr_error || r_read_error_sticky || r_write_error_sticky || (w_is_ctrlrd &amp;&amp; ctrlrd_error) || (w_is_ctrlwr &amp;&amp; ctrlwr_error)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rows = descriptor_error/wr_error   cols = wr_sticky/rd_path   pages = ctrl_err</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 28 of 32 cells are unreachable, and NOT for the usual reason. These are not physically impossible states -- they are states the instantiation forbids by tying inputs to constants. Of the four surviving cells, three are green, and the whole reachable surface is spanned by just descriptor_error and ctrl_err. For a DATA descriptor ctrl_err is 0 too, so on the sink w_hard_error REDUCES TO descriptor_error ALONE. A write response of SLVERR or DECERR on every beat of a transfer produces no fatal error, no CH_ERROR (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:380), and no error bit in the MonBus packet (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:1084) -- the channel reports success. The detection itself is real and complete (projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:951/:955/:964); only the wiring is missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>descriptor_error</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>descriptor fetch/validity fault, from descriptor_engine_beats inside the scheduler group -- LIVE on the sink</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_beats.sv:264, wired :289</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>wr_error</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>sched_wr_error as the scheduler sees it</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:163</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>wr_sticky</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>r_write_error_sticky -- latched from wr_error and nothing else</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:944</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>rd_path</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>sched_rd_error || r_read_error_sticky, folded: both derive from the same input</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:162, :943</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ctrl_err</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>(w_is_ctrlrd &amp;&amp; ctrlrd_error) || (w_is_ctrlwr &amp;&amp; ctrlwr_error) -- LIVE, but only for CTRL descriptors</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:980, driven projects/components/dmas/rapids/rtl/fub/ctrlrd_engine.sv:437</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    LEGITIMATE tie-off: the sink has no AXI read engine, so sched_rd_error is tied to '0 at the instantiation and r_read_error_sticky can never latch. rd_path is therefore identically 0 on this instance and every cell with rd_path=1 is unreachable. The sink's read done-strobes are tied off in the same block, which is what makes this legitimate rather than a second defect.</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:513</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    THE DEFECT: sched_wr_error reaches this scheduler from rapids_snk_beats, where it is assigned a constant '0 under a TODO claiming the write engine does not support error reporting -- which is false. So wr_error is identically 0 on this instance, and wr_sticky, whose only source is wr_error, is identically 0 with it. Every cell with either set is unreachable. Unlike the relation above, nothing about the sink's architecture requires this.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680, path :514 -&gt; projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_array_beats.sv:541 -&gt; projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_beats.sv:411 -&gt; projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:163</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these five. The timeout path is a SEPARATE disjunct at the FSM (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:380) and is mapped below; channel reset overrides both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>[ctrl_err=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>[ctrl_err=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: ctrl_err  |  descriptor_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (3 ones, 28 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      descriptor_error | wr_error | wr_sticky | rd_path | ctrl_err</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>CH_ERROR entry  (on the SINK instance)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:380</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>if (w_hard_error || w_timeout_escalate) w_next_state = CH_ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>rows = descriptor_error/wr_error   cols = ctrl_err/timeout_escalate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: With wr_error tied off, the sink's only routes into sticky CH_ERROR are a descriptor fault, a control-engine fault on a CTRL descriptor, and an escalated timeout. For the DATA descriptors that carry all the traffic, that leaves descriptor_error and timeout escalation. Note what this costs: a write that is being NAKed by the fabric is exactly the case the timeout was meant to catch, but a SLVERR arrives WITH a B response, so it counts as write progress and resets the timeout counter (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:920). Errored traffic therefore looks healthy to both mechanisms at once. NOT YET ESTABLISHED as a field failure -- no test drives a sink SLVERR today; a directed test returning SLVERR on one burst and checking the channel faults would settle it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>descriptor_error</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>the one always-live hard-error term on the sink</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_beats.sv:289</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>wr_error</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>sched_wr_error -- a bad write response reaching the scheduler</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:163</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>ctrl_err</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>control-engine error; live only for CTRL opcodes</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:980</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>timeout_escalate</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>w_timeout_escalate -- soft timeout promoted after cfg_sched_timeout_limit consecutive windows</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:970</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    wr_error is identically 0 on this instance for the reason given in map 1, so every cell with it set is unreachable. It is carried as an axis precisely so the map shows what the sink gives up.</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four, plus channel reset which takes priority over the whole branch (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:369-370).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: timeout_escalate  |  ctrl_err  |  descriptor_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (7 ones, 8 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      descriptor_error | wr_error | ctrl_err | timeout_escalate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>drain_read_decoded[ch]  (which channel drains)</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>drain_read_decoded = '0; if (drain_read &amp;&amp; drain_id &lt; NC) drain_read_decoded[drain_id] = 1'b1;</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>rows = drain_read/id_match   cols = id_in_range/ch_has_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: TASK-002 item 2, and the map states the limitation exactly. Two things are visible. (1) The decode is INDEPENDENT of ch_has_data: a drain is decoded to whichever channel drain_id names, whether or not it holds data -- safety is entirely the consumer's responsibility. (2) More importantly, drain_id is a SINGLE index and drain_read a SINGLE bit, so at most one channel's decode can assert in any cycle. Concurrent drains are excluded by the port shape, not by anything in this expression, which is why searching the module for a 'single read' guard finds nothing -- there is no logic to find. Supporting concurrency would mean widening drain_read/drain_id/drain_data to per-channel vectors. The fill side has the identical shape. This is an architectural simplification, not a bug (projects/components/dmas/rapids/known_issues/active/sink_sram_control.md keeps it Low priority).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>drain_read</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>the consumer asserts a drain this cycle</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>id_match</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>drain_id selects THIS channel</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:148</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>id_in_range</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>drain_id &lt; NC</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>ch_has_data</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>this channel actually holds drainable data -- NOT an input to the decode</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:157</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id_match means drain_id equals this channel's index, and a channel index is by definition &lt; NC, so id_match implies id_in_range. Cells with id_match=1 and id_in_range=0 are unreachable and marked X.</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four. NC is a parameter; the other channels' state cannot influence this channel's decode, which is the whole point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: drain_read &amp; id_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (2 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      drain_read &amp; id_match &amp; id_in_range</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>Where the sink's write error is lost, stage by stage</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>The RAPIDS SOURCE path is also correct (projects/components/dmas/rapids/rtl/macro_beats/rapids_src_beats.sv:491). The fix is to give the two sink data-path modules a sched_wr_error output, connect it, and replace the tie-off -- mirroring what the source and STREAM already do. Recorded in projects/components/dmas/rapids/known_issues/active/sink_data_path.md; the RTL change is the owner's call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>What happens to the error</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Citation</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>axi_write_engine_beats</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>DETECTED: bad B response latched sticky per channel, port driven</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:951 / :955 / :964</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>snk_data_path_beats</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>DISCARDED: connected to an empty port under the comment "Error and Debug (unconnected at this level)"</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>snk_data_path_beats.sv:269</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>snk_data_path_axis_beats / snk_data_path_beats</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>CANNOT PROPAGATE: neither module declares an error output; the only such output in RAPIDS is the engine's own</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:144</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>rapids_snk_beats</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>TIED OFF: assign sched_wr_error = '0, under a TODO whose stated reason is false</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680 -&gt; :514</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>scheduler_beats</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>DEAD TERMS: sched_wr_error and r_write_error_sticky are constant 0, in both w_hard_error and the MonBus error packet</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:944 / :979 / :1084</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>STREAM, for comparison</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>WIRED: declared, connected, no tie-off, and surfaced for observability as obs_flags[11]</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:669 / :1047 / :2130</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
+++ b/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
@@ -824,7 +824,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TARGET: TASK-002 item 3, the DRAIN_SIZE&gt;1 source beat drop (projects/components/dmas/rapids/known_issues/active/drain_size_gt1_source_beat_drop.md). The first map is the important one -- it is a map whose 1-cells include cells that should be impossible, and the axis that would have excluded them is not an input to the decision at all.</t>
+          <t>TARGET: rapids TASK-002 item 3, the DRAIN_SIZE&gt;1 source beat drop (projects/components/dmas/rapids/known_issues/active/drain_size_gt1_source_beat_drop.md). The first map is the important one -- it is a map whose 1-cells include cells that should be impossible, and the axis that would have excluded them is not an input to the decision at all.</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The sink admits network beats through a per-channel reservation counter (r_pending_alloc) that is incremented on a REQUEST to an allocator whose grant signal is discarded. This sheet is the contract for that interface. NOTE: TASK-002 item 5 names this target 'credit/RDA accounting'; neither exists in the RTL -- there are zero word-boundary RDA references and no credit machinery (scheduler_beats.sv says 'No credit management'). The real decision surface is ingress admission, mapped here.</t>
+          <t>The sink admits network beats through a per-channel reservation counter (r_pending_alloc) that is incremented on a REQUEST to an allocator whose grant signal is discarded. This sheet is the contract for that interface. NOTE: rapids TASK-002 item 5 names this target 'credit/RDA accounting'; neither exists in the RTL -- there are zero word-boundary RDA references and no credit machinery (scheduler_beats.sv says 'No credit management'). The real decision surface is ingress admission, mapped here.</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TARGET: TASK-002 item 5, re-scoped. The first map is the one that matters: it shows an AXIS beat being accepted on a term that does not include the only signal that decides whether the beat can be stored.</t>
+          <t>TARGET: rapids TASK-002 item 5, re-scoped. The first map is the one that matters: it shows an AXIS beat being accepted on a term that does not include the only signal that decides whether the beat can be stored.</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>RAPIDS' sink network side has no STREAM counterpart, so none of STREAM's proofs transfer here. That is exactly why TASK-002 ranks this the most exposed area, and it is the first sheet in this workbook with no fixed STREAM original to compare against.</t>
+          <t>RAPIDS' sink network side has no STREAM counterpart, so none of STREAM's proofs transfer here. That is exactly why rapids TASK-002 ranks this the most exposed area, and it is the first sheet in this workbook with no fixed STREAM original to compare against.</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TARGET: TASK-002 item 4. Unlike the alloc/drain FUBs (byte-identical to STREAM's), this module DIVERGED: 1150 lines against STREAM's 1390. Map 1 is where the divergence lives, and it is the cone of the resolved wedge in projects/components/dmas/rapids/known_issues/resolved/snk_scheduler_write_commit_stall.md.</t>
+          <t>TARGET: rapids TASK-002 item 4. Unlike the alloc/drain FUBs (byte-identical to STREAM's), this module DIVERGED: 1150 lines against STREAM's 1390. Map 1 is where the divergence lives, and it is the cone of the resolved wedge in projects/components/dmas/rapids/known_issues/resolved/snk_scheduler_write_commit_stall.md.</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>w_wr_need_base -- TASK-101 run-boundary stall</t>
+          <t>w_wr_need_base -- stream TASK-101 run-boundary stall</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TASK-002 items 1 and 2. Item 1: the write engine detects bad B responses per channel and the sink throws that detection away, leaving two fatal-error terms provably dead. Item 2: the sink SRAM drain port serves one channel per cycle by construction. Both were filed against retired pre-beats files, so only their anchors were stale; see projects/components/dmas/rapids/known_issues/active/sink_data_path.md and projects/components/dmas/rapids/known_issues/active/sink_sram_control.md.</t>
+          <t>rapids TASK-002 items 1 and 2. Item 1: the write engine detects bad B responses per channel, and the sink used to throw that detection away, leaving two fatal-error terms provably dead. FIXED 2026-09-25 -- the maps below show the repaired cone, with the defect kept as a recorded relation so the history is not lost. Item 2: the sink SRAM drain port serves one channel per cycle by construction. Both were filed against retired pre-beats files, so only their anchors were stale; see projects/components/dmas/rapids/known_issues/active/sink_data_path.md and projects/components/dmas/rapids/known_issues/active/sink_sram_control.md.</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>A SLVERR or DECERR on a write response must reach the channel FSM and fault the channel. It does not, on the sink.</t>
+          <t>A SLVERR or DECERR on a write response must reach the channel FSM and fault the channel. Since 2026-09-25 it does.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -4167,17 +4167,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Tied to a constant: `assign sched_wr_error = '0;` with the comment "TODO: Add when write engine supports error reporting".</t>
+          <t>Driven from the sink data path, which now exports the engine's sticky flag. FIXED 2026-09-25: this net was previously `assign sched_wr_error = '0;` under a TODO claiming the write engine did not support error reporting -- which was false.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>The TODO's stated reason is FALSE -- the engine has supported error reporting all along (see the row above). This net is what the scheduler actually sees.</t>
+          <t>Must carry the engine's per-channel flag, not a constant. It now does, so w_hard_error's sched_wr_error term and r_write_error_sticky are live on the sink.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680, consumed at :514 by the scheduler_group_array_beats instantiated at :344.</t>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:640 connects it, :514 feeds the scheduler_group_array_beats instantiated at :344. The data path exports it at projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_beats.sv:275.</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Constant 0 on the sink, because its only source is the tied-off net. Feeds w_hard_error AND the MonBus error packet, so the sink's error telemetry is dead too.</t>
+          <t>Was constant 0 on the sink while its only source was tied off; live since 2026-09-25. Feeds w_hard_error AND the MonBus error packet, so the sink's error telemetry works now too.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>On the sink, 4 of the 7 terms are constant 0. For a DATA descriptor it reduces to descriptor_error alone.</t>
+          <t>2 of the 7 terms are still constant 0 on the sink (sched_rd_error and r_read_error_sticky -- legitimately, there is no AXI read engine here). Before 2026-09-25 it was 4, and a DATA descriptor reduced to descriptor_error alone.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4390,7 +4390,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TARGET: TASK-002 items 1 and 2. READ THE X CELLS FIRST. Normally a don't-care marks a state that cannot physically occur. Here most of map 1 is X because inputs were tied to constants at an instantiation -- two legitimately, two by defect. The don't-cares ARE the finding.</t>
+          <t>TARGET: rapids TASK-002 items 1 and 2. READ THE X CELLS FIRST. Normally a don't-care marks a state that cannot physically occur. In map 1 they mark states the INSTANTIATION forbids by tying an input to a constant. That used to be four axes; two of those tie-offs were a defect, fixed 2026-09-25, so the map now shows 16 X cells rather than 28. The surviving exclusion is legitimate: the sink has no AXI read engine.</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: 28 of 32 cells are unreachable, and NOT for the usual reason. These are not physically impossible states -- they are states the instantiation forbids by tying inputs to constants. Of the four surviving cells, three are green, and the whole reachable surface is spanned by just descriptor_error and ctrl_err. For a DATA descriptor ctrl_err is 0 too, so on the sink w_hard_error REDUCES TO descriptor_error ALONE. A write response of SLVERR or DECERR on every beat of a transfer produces no fatal error, no CH_ERROR (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:380), and no error bit in the MonBus packet (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:1084) -- the channel reports success. The detection itself is real and complete (projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:951/:955/:964); only the wiring is missing.</t>
+          <t>CHECK BY INSPECTION: 16 of 32 cells are unreachable, and NOT for the usual reason: they are states the INSTANTIATION forbids by tying an input to a constant, not states that cannot physically occur. The one surviving exclusion is legitimate -- the sink has no AXI read engine, so rd_path is identically 0. Of the 16 reachable cells 15 are green: any single error term faults the channel. COMPARE THE PREVIOUS VERSION: until 2026-09-25 wr_error and wr_sticky were ALSO tied to 0, only 4 cells were reachable, and a SLVERR or DECERR on every beat of a transfer produced no fatal error, no CH_ERROR (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:380) and no error bit in the MonBus packet (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:1084) -- the channel reported success. The detection was always real (projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:951/:955/:964); only the wiring was missing, and it is now in place.</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4558,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    THE DEFECT: sched_wr_error reaches this scheduler from rapids_snk_beats, where it is assigned a constant '0 under a TODO claiming the write engine does not support error reporting -- which is false. So wr_error is identically 0 on this instance, and wr_sticky, whose only source is wr_error, is identically 0 with it. Every cell with either set is unreachable. Unlike the relation above, nothing about the sink's architecture requires this.</t>
+          <t xml:space="preserve">    (independent) HISTORY, no longer an exclusion: until 2026-09-25 sched_wr_error was assigned a constant '0 in rapids_snk_beats under a TODO claiming the write engine did not support error reporting -- which was false. wr_error and wr_sticky were therefore identically 0 and 28 of these 32 cells were unreachable, leaving a surface spanned by descriptor_error and ctrl_err alone. The sink data path now exports the engine's flag and the tie-off is gone, so those cells are REACHABLE and no predicate excludes them. Recorded as an independence note so the repair is visible in the map, not only in git.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680, path :514 -&gt; projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_array_beats.sv:541 -&gt; projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_beats.sv:411 -&gt; projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:163</t>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:640, path :514 -&gt; projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_array_beats.sv:541 -&gt; projects/components/dmas/rapids/rtl/macro_beats/scheduler_group_beats.sv:411 -&gt; projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:163; exported at projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_beats.sv:275</t>
         </is>
       </c>
     </row>
@@ -4622,10 +4622,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E23" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4634,25 +4632,21 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4661,25 +4655,21 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4701,10 +4691,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4755,10 +4743,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E30" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4767,25 +4753,21 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E31" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -4794,25 +4776,21 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E32" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -4834,23 +4812,21 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E33" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>DERIVED MINIMAL SOP: ctrl_err  |  descriptor_error</t>
+          <t>DERIVED MINIMAL SOP: ctrl_err  |  wr_sticky  |  wr_error  |  descriptor_error</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (3 ones, 28 don't-cares -- X cells were free to widen the cover)</t>
+          <t xml:space="preserve">  (15 ones, 16 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4873,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: With wr_error tied off, the sink's only routes into sticky CH_ERROR are a descriptor fault, a control-engine fault on a CTRL descriptor, and an escalated timeout. For the DATA descriptors that carry all the traffic, that leaves descriptor_error and timeout escalation. Note what this costs: a write that is being NAKed by the fabric is exactly the case the timeout was meant to catch, but a SLVERR arrives WITH a B response, so it counts as write progress and resets the timeout counter (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:920). Errored traffic therefore looks healthy to both mechanisms at once. NOT YET ESTABLISHED as a field failure -- no test drives a sink SLVERR today; a directed test returning SLVERR on one burst and checking the channel faults would settle it.</t>
+          <t>CHECK BY INSPECTION: No cell is excluded here any more: all four routes into sticky CH_ERROR are live on the sink since the wr_error wiring was restored on 2026-09-25. 15 of 16 cells are green -- any one fault takes the channel to CH_ERROR. The wr_error column is the part that was dead: previously every cell with it set was unreachable, so a bad write response could not fault the channel at all. One consequence is worth keeping in view even now: a SLVERR arrives WITH a B response, and the commit strobe is gated on bvalid/bready and BID with no bresp test (projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:898), so it still counts as write progress and resets the timeout counter (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:920). The error path catches it now, but the timeout never will -- which matters for a dropped burst that returns no B at all. That is gap 1 of the known issue and remains OPEN. NOT YET ESTABLISHED: no test drives a sink SLVERR today; a directed test returning SLVERR on one burst and checking the channel faults would close the loop.</t>
         </is>
       </c>
     </row>
@@ -5003,12 +4979,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    wr_error is identically 0 on this instance for the reason given in map 1, so every cell with it set is unreachable. It is carried as an axis precisely so the map shows what the sink gives up.</t>
+          <t xml:space="preserve">    (independent) wr_error USED to be identically 0 on this instance (see map 1), which made every cell carrying it unreachable. The tie-off is gone, so nothing is excluded here now. Kept as an independence note because the axis is only interesting once you know it was dead.</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680</t>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:640</t>
         </is>
       </c>
     </row>
@@ -5066,25 +5042,17 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="B56" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -5093,25 +5061,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="B57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5136,215 +5096,231 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>DERIVED MINIMAL SOP: timeout_escalate  |  ctrl_err  |  descriptor_error</t>
+          <t>DERIVED MINIMAL SOP: timeout_escalate  |  ctrl_err  |  wr_error  |  descriptor_error</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (7 ones, 8 don't-cares -- X cells were free to widen the cover)</t>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      descriptor_error | wr_error | ctrl_err | timeout_escalate</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>RTL AS WRITTEN:      descriptor_error | wr_error | ctrl_err | timeout_escalate</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="inlineStr">
-        <is>
-          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>drain_read_decoded[ch]  (which channel drains)</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>drain_read_decoded[ch]  (which channel drains)</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>drain_read_decoded = '0; if (drain_read &amp;&amp; drain_id &lt; NC) drain_read_decoded[drain_id] = 1'b1;</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>drain_read_decoded = '0; if (drain_read &amp;&amp; drain_id &lt; NC) drain_read_decoded[drain_id] = 1'b1;</t>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>rows = drain_read/id_match   cols = id_in_range/ch_has_data</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>rows = drain_read/id_match   cols = id_in_range/ch_has_data</t>
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: rapids TASK-002 item 2, and the map states the limitation exactly. Two things are visible. (1) The decode is INDEPENDENT of ch_has_data: a drain is decoded to whichever channel drain_id names, whether or not it holds data -- safety is entirely the consumer's responsibility. (2) More importantly, drain_id is a SINGLE index and drain_read a SINGLE bit, so at most one channel's decode can assert in any cycle. Concurrent drains are excluded by the port shape, not by anything in this expression, which is why searching the module for a 'single read' guard finds nothing -- there is no logic to find. Supporting concurrency would mean widening drain_read/drain_id/drain_data to per-channel vectors. The fill side has the identical shape. This is an architectural simplification, not a bug (projects/components/dmas/rapids/known_issues/active/sink_sram_control.md keeps it Low priority).</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: TASK-002 item 2, and the map states the limitation exactly. Two things are visible. (1) The decode is INDEPENDENT of ch_has_data: a drain is decoded to whichever channel drain_id names, whether or not it holds data -- safety is entirely the consumer's responsibility. (2) More importantly, drain_id is a SINGLE index and drain_read a SINGLE bit, so at most one channel's decode can assert in any cycle. Concurrent drains are excluded by the port shape, not by anything in this expression, which is why searching the module for a 'single read' guard finds nothing -- there is no logic to find. Supporting concurrency would mean widening drain_read/drain_id/drain_data to per-channel vectors. The fill side has the identical shape. This is an architectural simplification, not a bug (projects/components/dmas/rapids/known_issues/active/sink_sram_control.md keeps it Low priority).</t>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>AXES</t>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>axis</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>defining expression</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>cite</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>drain_read</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>the consumer asserts a drain this cycle</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>drain_read</t>
+          <t>id_match</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>the consumer asserts a drain this cycle</t>
+          <t>drain_id selects THIS channel</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:148</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>id_match</t>
+          <t>id_in_range</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>drain_id selects THIS channel</t>
+          <t>drain_id &lt; NC</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:148</t>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>id_in_range</t>
+          <t>ch_has_data</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>drain_id &lt; NC</t>
+          <t>this channel actually holds drainable data -- NOT an input to the decode</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:157</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    id_match means drain_id equals this channel's index, and a channel index is by definition &lt; NC, so id_match implies id_in_range. Cells with id_match=1 and id_in_range=0 are unreachable and marked X.</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
           <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>ch_has_data</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>this channel actually holds drainable data -- NOT an input to the decode</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:157</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    id_match means drain_id equals this channel's index, and a channel index is by definition &lt; NC, so id_match implies id_in_range. Cells with id_match=1 and id_in_range=0 are unreachable and marked X.</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_sram_controller_beats.sv:147</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
           <t>DEPENDS ONLY ON: these four. NC is a parameter; the other channels' state cannot influence this channel's decode, which is the whole point.</t>
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
     <row r="79">
-      <c r="B79" s="10" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="11" t="n">
-        <v>0</v>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="D80" s="11" t="n">
         <v>0</v>
@@ -5356,7 +5332,7 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
@@ -5369,216 +5345,193 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>0</v>
+      <c r="D81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D82" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B83" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="11" t="n">
-        <v>0</v>
+      <c r="B82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: drain_read &amp; id_match</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: drain_read &amp; id_match</t>
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (2 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (2 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      drain_read &amp; id_match &amp; id_in_range</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>RTL AS WRITTEN:      drain_read &amp; id_match &amp; id_in_range</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="15" t="inlineStr">
+      <c r="A87" s="15" t="inlineStr">
         <is>
           <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>How the sink's write error reaches the scheduler (FIXED 2026-09-25)</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:640</t>
+        </is>
+      </c>
+    </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>Where the sink's write error is lost, stage by stage</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680</t>
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Applied 2026-09-25, mirroring what the RAPIDS source path (projects/components/dmas/rapids/rtl/macro_beats/rapids_src_beats.sv:491) and STREAM already did. Verilator lint is warning-for-warning identical to the pre-change baseline. Gap 1 of the known issue is NOT fixed: there is still no AXI transaction timeout in axi_write_engine_beats, and that file is byte-identical with STREAM's. See projects/components/dmas/rapids/known_issues/active/sink_data_path.md.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>The RAPIDS SOURCE path is also correct (projects/components/dmas/rapids/rtl/macro_beats/rapids_src_beats.sv:491). The fix is to give the two sink data-path modules a sched_wr_error output, connect it, and replace the tie-off -- mirroring what the source and STREAM already do. Recorded in projects/components/dmas/rapids/known_issues/active/sink_data_path.md; the RTL change is the owner's call.</t>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>What happens to the error</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Citation</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>What happens to the error</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>Citation</t>
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>axi_write_engine_beats</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>DETECTED: bad B response latched sticky per channel, port driven</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:951 / :955 / :964</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>axi_write_engine_beats</t>
+          <t>snk_data_path_beats</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>DETECTED: bad B response latched sticky per channel, port driven</t>
+          <t>EXPORTED: was connected to an empty port under "Error and Debug (unconnected at this level)"; now declares a sched_wr_error output and drives it</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:951 / :955 / :964</t>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/snk_data_path_beats.sv:275</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>snk_data_path_beats</t>
+          <t>snk_data_path_axis_beats</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>DISCARDED: connected to an empty port under the comment "Error and Debug (unconnected at this level)"</t>
+          <t>PASSED THROUGH: gained a matching sched_wr_error output. Before the fix neither wrapper declared one, so the flag could not propagate even in principle</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>snk_data_path_beats.sv:269</t>
+          <t>snk_data_path_axis_beats.sv port list</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>snk_data_path_axis_beats / snk_data_path_beats</t>
+          <t>rapids_snk_beats</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>CANNOT PROPAGATE: neither module declares an error output; the only such output in RAPIDS is the engine's own</t>
+          <t>CONNECTED: the assign sched_wr_error = '0 tie-off and its false TODO are deleted; the net is driven by the data path</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:144</t>
+          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:640 -&gt; :514</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>rapids_snk_beats</t>
+          <t>scheduler_beats</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>TIED OFF: assign sched_wr_error = '0, under a TODO whose stated reason is false</t>
+          <t>LIVE TERMS: sched_wr_error and r_write_error_sticky now carry the engine's flag, in both w_hard_error and the MonBus error packet</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/rapids/rtl/macro_beats/rapids_snk_beats.sv:680 -&gt; :514</t>
+          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:944 / :979 / :1084</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>scheduler_beats</t>
+          <t>STREAM, for comparison</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>DEAD TERMS: sched_wr_error and r_write_error_sticky are constant 0, in both w_hard_error and the MonBus error packet</t>
+          <t>WIRED: declared, connected, no tie-off, and surfaced for observability as obs_flags[11]</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:944 / :979 / :1084</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>STREAM, for comparison</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>WIRED: declared, connected, no tie-off, and surfaced for observability as obs_flags[11]</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:669 / :1047 / :2130</t>
         </is>

--- a/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
+++ b/projects/components/dmas/rapids/docs/rapids_signal_contracts.xlsx
@@ -4873,7 +4873,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: No cell is excluded here any more: all four routes into sticky CH_ERROR are live on the sink since the wr_error wiring was restored on 2026-09-25. 15 of 16 cells are green -- any one fault takes the channel to CH_ERROR. The wr_error column is the part that was dead: previously every cell with it set was unreachable, so a bad write response could not fault the channel at all. One consequence is worth keeping in view even now: a SLVERR arrives WITH a B response, and the commit strobe is gated on bvalid/bready and BID with no bresp test (projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:898), so it still counts as write progress and resets the timeout counter (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:920). The error path catches it now, but the timeout never will -- which matters for a dropped burst that returns no B at all. That is gap 1 of the known issue and remains OPEN. NOT YET ESTABLISHED: no test drives a sink SLVERR today; a directed test returning SLVERR on one burst and checking the channel faults would close the loop.</t>
+          <t>CHECK BY INSPECTION: No cell is excluded here any more: all four routes into sticky CH_ERROR are live on the sink since the wr_error wiring was restored on 2026-09-25. 15 of 16 cells are green -- any one fault takes the channel to CH_ERROR. The wr_error column is the part that was dead: previously every cell with it set was unreachable, so a bad write response could not fault the channel at all. One consequence is worth keeping in view even now: a SLVERR arrives WITH a B response, and the commit strobe is gated on bvalid/bready and BID with no bresp test (projects/components/dmas/rapids/rtl/fub_beats/axi_write_engine_beats.sv:898), so it still counts as write progress and resets the timeout counter (projects/components/dmas/rapids/rtl/fub_beats/scheduler_beats.sv:920). The error path catches it now. A burst that returns no B at all is a different mechanism and is NOT this cone's job: AXI transaction timeouts are detected by the monitor layer by design (rtl/amba/monitor/axi_monitor_timer.sv plus axi_monitor_reporter_timeout.sv, gated by cfg_timeout_enable), not by a counter in the engine. NOT YET ESTABLISHED: no test drives a sink SLVERR today; a directed test returning SLVERR on one burst and checking the channel faults would close the loop.</t>
         </is>
       </c>
     </row>
